--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261019.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261019.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>620,600</t>
+          <t>1,408,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,408,000</t>
+          <t>620,600</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>447,000</t>
+          <t>318,672</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>318,672</t>
+          <t>447,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202610WTEV6F</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,017,822</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>202610WTEV6F</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1,017,822</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>148,921</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>148,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>7,285,249</t>
+          <t>148,386</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>148,386</t>
+          <t>7,285,249</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>325,000</t>
+          <t>295,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>295,000</t>
+          <t>325,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>770,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>185,000</t>
+          <t>770,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>1,786,000</t>
+          <t>1,147,121</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,147,121</t>
+          <t>1,786,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>337,000</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>202611WVHFX6F</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>173,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>117,000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>202611WVHFX6F</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>421,000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>173,000</t>
+          <t>337,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>421,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>258,000</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>159,000</t>
+          <t>691,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>691,000</t>
+          <t>258,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>181,000</t>
+          <t>159,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>116,000</t>
+          <t>73,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -2229,17 +2229,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>73,000</t>
+          <t>116,000</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
